--- a/tests/testthat/fixtures/ex3/tables/irt_poly_booklet2.xlsx
+++ b/tests/testthat/fixtures/ex3/tables/irt_poly_booklet2.xlsx
@@ -154,22 +154,22 @@
     <t xml:space="preserve">step3</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17 (0.112)</t>
+    <t xml:space="preserve">0.17 (0.11)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.17</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77 (0.12)</t>
+    <t xml:space="preserve">0.77 (0.10)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.77</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39 (0.122)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.03 (0.142)</t>
+    <t xml:space="preserve">1.39 (0.12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.03 (0.14)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.36</t>
